--- a/WEEK6/cara kerja perhitungan naive bayes.xlsx
+++ b/WEEK6/cara kerja perhitungan naive bayes.xlsx
@@ -1,14 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\Machine-Learning\WEEK6\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F724239-171E-43ED-97DC-6AB0834FA8FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Data NB" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Quiz NB" sheetId="2" r:id="rId5"/>
+    <sheet name="Data NB" sheetId="1" r:id="rId1"/>
+    <sheet name="Quiz NB" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="IvpxLtgn7pUZIyLtdHDuz36NTvFsaIEOlEZOQPYI0Uc="/>
     </ext>
@@ -17,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="80">
   <si>
     <t xml:space="preserve">Cara Kerja Naive Bayes Classification </t>
   </si>
@@ -186,17 +204,18 @@
   <si>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
-        <color theme="1"/>
       </rPr>
       <t xml:space="preserve">adalah: </t>
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
-        <b/>
-        <color theme="1"/>
-        <sz val="11.0"/>
       </rPr>
       <t>"No"</t>
     </r>
@@ -222,43 +241,43 @@
   <si>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
       </rPr>
       <t xml:space="preserve">Berdasarkan data di atas, gunakan algoritma </t>
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
-        <b/>
-        <color theme="1"/>
-        <sz val="11.0"/>
       </rPr>
       <t>Naive Bayes</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
       </rPr>
       <t xml:space="preserve"> untuk memprediksi apakah seseorang akan </t>
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
-        <b/>
-        <color theme="1"/>
-        <sz val="11.0"/>
       </rPr>
       <t>Play = Yes atau No</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
       </rPr>
       <t xml:space="preserve"> jika kondisi cuaca berikut:</t>
     </r>
@@ -289,12 +308,36 @@
   </si>
   <si>
     <t>- Tentukan prediksi akhir berdasarkan probabilitas tertinggi</t>
+  </si>
+  <si>
+    <t>No(4)</t>
+  </si>
+  <si>
+    <t>4/8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P(Weak|Yes) = </t>
+  </si>
+  <si>
+    <t xml:space="preserve">P(Weak|No) = </t>
+  </si>
+  <si>
+    <t>Outlook = Sunny, Temperature = Cool, Humidity = High, Wind = Weak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gunakan Laplace smoothing: (0+1)/(4+4) </t>
+  </si>
+  <si>
+    <t>Roni Gunawan Muhammad</t>
+  </si>
+  <si>
+    <t>Robotika A Malam</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#\ ?/4"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0.00000_);_(* \(#,##0.00000\);_(* &quot;-&quot;?????_);_(@_)"/>
@@ -302,59 +345,60 @@
   </numFmts>
   <fonts count="10">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13.0"/>
+      <sz val="13"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arimo"/>
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
     </font>
@@ -364,11 +408,17 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
-    <border/>
+  <borders count="4">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -382,94 +432,143 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+  <cellXfs count="39">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="12" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="12" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="166" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="16" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="12" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="12" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -659,642 +758,670 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:I1000"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="8.71"/>
-    <col customWidth="1" min="2" max="2" width="14.29"/>
-    <col customWidth="1" min="3" max="3" width="12.29"/>
-    <col customWidth="1" min="4" max="4" width="12.57"/>
-    <col customWidth="1" min="5" max="5" width="8.71"/>
-    <col customWidth="1" min="6" max="6" width="12.29"/>
-    <col customWidth="1" min="7" max="26" width="8.71"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+    <col min="7" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1"/>
-    <row r="2" ht="14.25" customHeight="1"/>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="B3" s="1" t="s">
+    <row r="1" spans="2:9" ht="14.25" customHeight="1"/>
+    <row r="2" spans="2:9" ht="14.25" customHeight="1"/>
+    <row r="3" spans="2:9" ht="14.25" customHeight="1">
+      <c r="B3" s="21" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" ht="14.25" customHeight="1"/>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="B5" s="2" t="s">
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+    </row>
+    <row r="4" spans="2:9" ht="14.25" customHeight="1"/>
+    <row r="5" spans="2:9" ht="14.25" customHeight="1">
+      <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1"/>
-    <row r="7" ht="14.25" customHeight="1">
-      <c r="B7" s="3" t="s">
+    <row r="6" spans="2:9" ht="14.25" customHeight="1"/>
+    <row r="7" spans="2:9" ht="14.25" customHeight="1">
+      <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" ht="14.25" customHeight="1">
-      <c r="B8" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="I7" s="29"/>
+    </row>
+    <row r="8" spans="2:9" ht="14.25" customHeight="1">
+      <c r="B8" s="3">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" ht="14.25" customHeight="1">
-      <c r="B9" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="I8" s="30"/>
+    </row>
+    <row r="9" spans="2:9" ht="14.25" customHeight="1">
+      <c r="B9" s="3">
+        <v>2</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="B10" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="C10" s="4" t="s">
+    <row r="10" spans="2:9" ht="14.25" customHeight="1">
+      <c r="B10" s="3">
+        <v>3</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="B11" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="C11" s="4" t="s">
+    <row r="11" spans="2:9" ht="14.25" customHeight="1">
+      <c r="B11" s="3">
+        <v>4</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="B12" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="C12" s="4" t="s">
+    <row r="12" spans="2:9" ht="14.25" customHeight="1">
+      <c r="B12" s="3">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" ht="14.25" customHeight="1">
-      <c r="B13" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="C13" s="4" t="s">
+    <row r="13" spans="2:9" ht="14.25" customHeight="1">
+      <c r="B13" s="3">
+        <v>6</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" ht="14.25" customHeight="1">
-      <c r="B14" s="4">
-        <v>7.0</v>
-      </c>
-      <c r="C14" s="4" t="s">
+    <row r="14" spans="2:9" ht="14.25" customHeight="1">
+      <c r="B14" s="3">
+        <v>7</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" ht="14.25" customHeight="1"/>
-    <row r="16" ht="14.25" customHeight="1"/>
-    <row r="17" ht="14.25" customHeight="1">
-      <c r="B17" s="2" t="s">
+    <row r="15" spans="2:9" ht="14.25" customHeight="1"/>
+    <row r="16" spans="2:9" ht="14.25" customHeight="1"/>
+    <row r="17" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B17" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" ht="14.25" customHeight="1"/>
-    <row r="19" ht="14.25" customHeight="1">
-      <c r="B19" s="5" t="s">
+    <row r="18" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="19" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B19" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="5">
         <f>4/7</f>
-        <v>0.5714285714</v>
-      </c>
-    </row>
-    <row r="20" ht="14.25" customHeight="1">
-      <c r="B20" s="5" t="s">
+        <v>0.5714285714285714</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B20" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="5">
         <f>3/7</f>
-        <v>0.4285714286</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25" customHeight="1"/>
-    <row r="22" ht="14.25" customHeight="1"/>
-    <row r="23" ht="14.25" customHeight="1">
-      <c r="B23" s="2" t="s">
+        <v>0.42857142857142855</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="22" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="23" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B23" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" ht="14.25" customHeight="1">
-      <c r="B24" s="7" t="s">
+    <row r="24" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B24" s="23" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="25" ht="14.25" customHeight="1"/>
-    <row r="26" ht="14.25" customHeight="1">
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-    </row>
-    <row r="27" ht="14.25" customHeight="1">
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-    </row>
-    <row r="28" ht="14.25" customHeight="1"/>
-    <row r="29" ht="14.25" customHeight="1">
-      <c r="B29" s="5" t="s">
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+    </row>
+    <row r="25" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+    </row>
+    <row r="26" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+    </row>
+    <row r="27" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+    </row>
+    <row r="28" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="29" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B29" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="F29" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="30" ht="14.25" customHeight="1"/>
-    <row r="31" ht="14.25" customHeight="1">
-      <c r="B31" s="4" t="s">
+    <row r="30" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="31" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B31" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="F31" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="H31" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" ht="14.25" customHeight="1">
-      <c r="B32" s="4" t="s">
+    <row r="32" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C32" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="D32" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="F32" s="9" t="s">
+      <c r="C32" s="3">
+        <v>0</v>
+      </c>
+      <c r="D32" s="3">
+        <v>2</v>
+      </c>
+      <c r="F32" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G32" s="9">
-        <v>1.0</v>
-      </c>
-      <c r="H32" s="9">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="33" ht="14.25" customHeight="1">
-      <c r="B33" s="4" t="s">
+      <c r="G32" s="7">
+        <v>1</v>
+      </c>
+      <c r="H32" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B33" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="D33" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="F33" s="9" t="s">
+      <c r="C33" s="3">
+        <v>2</v>
+      </c>
+      <c r="D33" s="3">
+        <v>1</v>
+      </c>
+      <c r="F33" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G33" s="9">
-        <v>1.0</v>
-      </c>
-      <c r="H33" s="9">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="34" ht="14.25" customHeight="1">
-      <c r="B34" s="4" t="s">
+      <c r="G33" s="7">
+        <v>1</v>
+      </c>
+      <c r="H33" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B34" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="D34" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="F34" s="9" t="s">
+      <c r="C34" s="3">
+        <v>2</v>
+      </c>
+      <c r="D34" s="3">
+        <v>0</v>
+      </c>
+      <c r="F34" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G34" s="9">
-        <v>2.0</v>
-      </c>
-      <c r="H34" s="9">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="35" ht="14.25" customHeight="1"/>
-    <row r="36" ht="14.25" customHeight="1"/>
-    <row r="37" ht="14.25" customHeight="1">
-      <c r="B37" s="10" t="s">
+      <c r="G34" s="7">
+        <v>2</v>
+      </c>
+      <c r="H34" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="36" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="37" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B37" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="F37" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" ht="14.25" customHeight="1"/>
-    <row r="39" ht="14.25" customHeight="1">
-      <c r="B39" s="9" t="s">
+    <row r="38" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="39" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B39" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D39" s="9" t="s">
+      <c r="D39" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F39" s="9" t="s">
+      <c r="F39" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G39" s="9" t="s">
+      <c r="G39" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H39" s="9" t="s">
+      <c r="H39" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="40" ht="14.25" customHeight="1">
-      <c r="B40" s="9" t="s">
+    <row r="40" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B40" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C40" s="9">
-        <v>2.0</v>
-      </c>
-      <c r="D40" s="9">
-        <v>2.0</v>
-      </c>
-      <c r="F40" s="9" t="s">
+      <c r="C40" s="7">
+        <v>2</v>
+      </c>
+      <c r="D40" s="7">
+        <v>2</v>
+      </c>
+      <c r="F40" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G40" s="9">
-        <v>3.0</v>
-      </c>
-      <c r="H40" s="9">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="41" ht="14.25" customHeight="1">
-      <c r="B41" s="9" t="s">
+      <c r="G40" s="7">
+        <v>3</v>
+      </c>
+      <c r="H40" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B41" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C41" s="9">
-        <v>2.0</v>
-      </c>
-      <c r="D41" s="9">
-        <v>1.0</v>
-      </c>
-      <c r="F41" s="9" t="s">
+      <c r="C41" s="7">
+        <v>2</v>
+      </c>
+      <c r="D41" s="7">
+        <v>1</v>
+      </c>
+      <c r="F41" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G41" s="9">
-        <v>1.0</v>
-      </c>
-      <c r="H41" s="9">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="42" ht="14.25" customHeight="1"/>
-    <row r="43" ht="14.25" customHeight="1"/>
-    <row r="44" ht="14.25" customHeight="1"/>
-    <row r="45" ht="14.25" customHeight="1">
-      <c r="B45" s="2" t="s">
+      <c r="G41" s="7">
+        <v>1</v>
+      </c>
+      <c r="H41" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="43" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="44" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="45" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B45" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="46" ht="14.25" customHeight="1">
-      <c r="B46" s="5" t="s">
+    <row r="46" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B46" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="47" ht="14.25" customHeight="1">
-      <c r="B47" s="11" t="s">
+    <row r="47" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B47" s="24" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="48" ht="14.25" customHeight="1"/>
-    <row r="49" ht="14.25" customHeight="1">
-      <c r="B49" s="2" t="s">
+      <c r="C47" s="22"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="22"/>
+    </row>
+    <row r="48" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="49" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B49" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-    </row>
-    <row r="50" ht="14.25" customHeight="1">
-      <c r="B50" s="2" t="s">
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+    </row>
+    <row r="50" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B50" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-    </row>
-    <row r="51" ht="14.25" customHeight="1"/>
-    <row r="52" ht="14.25" customHeight="1">
-      <c r="B52" s="5" t="s">
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+    </row>
+    <row r="51" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="52" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B52" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C52" s="6">
+      <c r="C52" s="5">
         <f>4/7</f>
-        <v>0.5714285714</v>
-      </c>
-    </row>
-    <row r="53" ht="14.25" customHeight="1">
-      <c r="B53" s="5" t="s">
+        <v>0.5714285714285714</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B53" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C53" s="5">
+      <c r="C53" s="4">
         <f>0/4</f>
         <v>0</v>
       </c>
-      <c r="D53" s="12" t="s">
+      <c r="D53" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="H53" s="6">
-        <f> 1/7</f>
-        <v>0.1428571429</v>
-      </c>
-    </row>
-    <row r="54" ht="14.25" customHeight="1">
-      <c r="B54" s="5" t="s">
+      <c r="E53" s="22"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="22"/>
+      <c r="H53" s="5">
+        <f>1/7</f>
+        <v>0.14285714285714285</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B54" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C54" s="13">
-        <f t="shared" ref="C54:C55" si="1">2/4</f>
+      <c r="C54" s="9">
+        <f t="shared" ref="C54:C55" si="0">2/4</f>
         <v>0.5</v>
       </c>
     </row>
-    <row r="55" ht="14.25" customHeight="1">
-      <c r="B55" s="5" t="s">
+    <row r="55" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B55" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C55" s="13">
-        <f t="shared" si="1"/>
+      <c r="C55" s="9">
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
     </row>
-    <row r="56" ht="14.25" customHeight="1">
-      <c r="B56" s="5" t="s">
+    <row r="56" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B56" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C56" s="6">
+      <c r="C56" s="5">
         <f>1/4</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="57" ht="14.25" customHeight="1"/>
-    <row r="58" ht="14.25" customHeight="1">
-      <c r="B58" s="5" t="s">
+    <row r="57" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="58" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B58" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C58" s="14">
+      <c r="C58" s="10">
         <f>C52*H53*C54*C55*C56</f>
-        <v>0.005102040816</v>
-      </c>
-    </row>
-    <row r="59" ht="14.25" customHeight="1"/>
-    <row r="60" ht="14.25" customHeight="1"/>
-    <row r="61" ht="14.25" customHeight="1">
-      <c r="B61" s="2" t="s">
+        <v>5.1020408163265302E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="60" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="61" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B61" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-    </row>
-    <row r="62" ht="14.25" customHeight="1"/>
-    <row r="63" ht="14.25" customHeight="1">
-      <c r="B63" s="5" t="s">
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+    </row>
+    <row r="62" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="63" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B63" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C63" s="6">
+      <c r="C63" s="5">
         <f>3/7</f>
-        <v>0.4285714286</v>
-      </c>
-    </row>
-    <row r="64" ht="14.25" customHeight="1">
-      <c r="B64" s="5" t="s">
+        <v>0.42857142857142855</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" ht="14.25" customHeight="1">
+      <c r="B64" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C64" s="6">
+      <c r="C64" s="5">
         <f>2/3</f>
-        <v>0.6666666667</v>
-      </c>
-    </row>
-    <row r="65" ht="14.25" customHeight="1">
-      <c r="B65" s="5" t="s">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" ht="14.25" customHeight="1">
+      <c r="B65" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C65" s="6">
-        <v>0.3333333333333333</v>
-      </c>
-    </row>
-    <row r="66" ht="14.25" customHeight="1">
-      <c r="B66" s="5" t="s">
+      <c r="C65" s="5">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="66" spans="2:7" ht="14.25" customHeight="1">
+      <c r="B66" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C66" s="6">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="67" ht="14.25" customHeight="1">
-      <c r="B67" s="5" t="s">
+      <c r="C66" s="5">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" ht="14.25" customHeight="1">
+      <c r="B67" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C67" s="6">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="68" ht="14.25" customHeight="1"/>
-    <row r="69" ht="14.25" customHeight="1">
-      <c r="B69" s="5" t="s">
+      <c r="C67" s="5">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="68" spans="2:7" ht="14.25" customHeight="1"/>
+    <row r="69" spans="2:7" ht="14.25" customHeight="1">
+      <c r="B69" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C69" s="14">
+      <c r="C69" s="10">
         <f>C63*C64*C65*C66*C67</f>
-        <v>0.04232804233</v>
-      </c>
-    </row>
-    <row r="70" ht="14.25" customHeight="1"/>
-    <row r="71" ht="14.25" customHeight="1">
-      <c r="B71" s="2" t="s">
+        <v>4.2328042328042326E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7" ht="14.25" customHeight="1"/>
+    <row r="71" spans="2:7" ht="14.25" customHeight="1">
+      <c r="B71" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="72" ht="14.25" customHeight="1"/>
-    <row r="73" ht="14.25" customHeight="1">
-      <c r="B73" s="15" t="s">
+    <row r="72" spans="2:7" ht="14.25" customHeight="1"/>
+    <row r="73" spans="2:7" ht="14.25" customHeight="1">
+      <c r="B73" s="11" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="74" ht="14.25" customHeight="1"/>
-    <row r="75" ht="14.25" customHeight="1">
-      <c r="B75" s="5" t="s">
+    <row r="74" spans="2:7" ht="14.25" customHeight="1"/>
+    <row r="75" spans="2:7" ht="14.25" customHeight="1">
+      <c r="B75" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="76" ht="14.25" customHeight="1">
-      <c r="B76" s="16"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-    </row>
-    <row r="77" ht="14.25" customHeight="1">
-      <c r="B77" s="17" t="s">
+    <row r="76" spans="2:7" ht="14.25" customHeight="1">
+      <c r="B76" s="12"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+    </row>
+    <row r="77" spans="2:7" ht="14.25" customHeight="1">
+      <c r="B77" s="13" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="78" ht="14.25" customHeight="1"/>
-    <row r="79" ht="14.25" customHeight="1">
-      <c r="B79" s="5" t="s">
+    <row r="78" spans="2:7" ht="14.25" customHeight="1"/>
+    <row r="79" spans="2:7" ht="14.25" customHeight="1">
+      <c r="B79" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="80" ht="14.25" customHeight="1"/>
-    <row r="81" ht="14.25" customHeight="1">
-      <c r="D81" s="18"/>
-    </row>
-    <row r="82" ht="14.25" customHeight="1">
-      <c r="D82" s="19"/>
-    </row>
-    <row r="83" ht="14.25" customHeight="1"/>
-    <row r="84" ht="14.25" customHeight="1"/>
-    <row r="85" ht="14.25" customHeight="1"/>
-    <row r="86" ht="14.25" customHeight="1"/>
-    <row r="87" ht="14.25" customHeight="1"/>
-    <row r="88" ht="14.25" customHeight="1"/>
-    <row r="89" ht="14.25" customHeight="1"/>
-    <row r="90" ht="14.25" customHeight="1"/>
-    <row r="91" ht="14.25" customHeight="1"/>
-    <row r="92" ht="14.25" customHeight="1"/>
-    <row r="93" ht="14.25" customHeight="1"/>
-    <row r="94" ht="14.25" customHeight="1"/>
-    <row r="95" ht="14.25" customHeight="1"/>
-    <row r="96" ht="14.25" customHeight="1"/>
+    <row r="80" spans="2:7" ht="14.25" customHeight="1"/>
+    <row r="81" spans="4:4" ht="14.25" customHeight="1">
+      <c r="D81" s="14"/>
+    </row>
+    <row r="82" spans="4:4" ht="14.25" customHeight="1">
+      <c r="D82" s="15"/>
+    </row>
+    <row r="83" spans="4:4" ht="14.25" customHeight="1"/>
+    <row r="84" spans="4:4" ht="14.25" customHeight="1"/>
+    <row r="85" spans="4:4" ht="14.25" customHeight="1"/>
+    <row r="86" spans="4:4" ht="14.25" customHeight="1"/>
+    <row r="87" spans="4:4" ht="14.25" customHeight="1"/>
+    <row r="88" spans="4:4" ht="14.25" customHeight="1"/>
+    <row r="89" spans="4:4" ht="14.25" customHeight="1"/>
+    <row r="90" spans="4:4" ht="14.25" customHeight="1"/>
+    <row r="91" spans="4:4" ht="14.25" customHeight="1"/>
+    <row r="92" spans="4:4" ht="14.25" customHeight="1"/>
+    <row r="93" spans="4:4" ht="14.25" customHeight="1"/>
+    <row r="94" spans="4:4" ht="14.25" customHeight="1"/>
+    <row r="95" spans="4:4" ht="14.25" customHeight="1"/>
+    <row r="96" spans="4:4" ht="14.25" customHeight="1"/>
     <row r="97" ht="14.25" customHeight="1"/>
     <row r="98" ht="14.25" customHeight="1"/>
     <row r="99" ht="14.25" customHeight="1"/>
@@ -2206,355 +2333,682 @@
     <mergeCell ref="B47:G47"/>
     <mergeCell ref="D53:G53"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <dimension ref="C1:V1000"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="4" width="8.71"/>
-    <col customWidth="1" min="5" max="5" width="13.14"/>
-    <col customWidth="1" min="6" max="26" width="8.71"/>
+    <col min="1" max="2" width="8.6640625" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" customWidth="1"/>
+    <col min="5" max="5" width="13.109375" customWidth="1"/>
+    <col min="6" max="13" width="8.6640625" customWidth="1"/>
+    <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1"/>
-    <row r="2" ht="14.25" customHeight="1">
-      <c r="C2" s="20" t="s">
+    <row r="1" spans="3:16" ht="14.25" customHeight="1"/>
+    <row r="2" spans="3:16" ht="14.25" customHeight="1">
+      <c r="C2" s="26" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" ht="14.25" customHeight="1"/>
-    <row r="4" ht="14.25" customHeight="1">
-      <c r="C4" s="5" t="s">
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+    </row>
+    <row r="3" spans="3:16" ht="14.25" customHeight="1"/>
+    <row r="4" spans="3:16" ht="14.25" customHeight="1">
+      <c r="C4" s="4" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="C5" s="5" t="s">
+      <c r="D4" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+    </row>
+    <row r="5" spans="3:16" ht="14.25" customHeight="1">
+      <c r="C5" s="4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="6" ht="14.25" customHeight="1">
-      <c r="C6" s="5" t="s">
+      <c r="D5" s="28">
+        <v>4222311024</v>
+      </c>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+    </row>
+    <row r="6" spans="3:16" ht="14.25" customHeight="1">
+      <c r="C6" s="4" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="7" ht="14.25" customHeight="1"/>
-    <row r="8" ht="14.25" customHeight="1">
-      <c r="C8" s="2" t="s">
+      <c r="D6" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+    </row>
+    <row r="7" spans="3:16" ht="14.25" customHeight="1"/>
+    <row r="8" spans="3:16" ht="14.25" customHeight="1">
+      <c r="C8" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="9" ht="14.25" customHeight="1"/>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="C10" s="21" t="s">
+    <row r="9" spans="3:16" ht="14.25" customHeight="1"/>
+    <row r="10" spans="3:16" ht="14.25" customHeight="1">
+      <c r="C10" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H10" s="21" t="s">
+      <c r="H10" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="C11" s="22">
-        <v>1.0</v>
-      </c>
-      <c r="D11" s="22" t="s">
+    <row r="11" spans="3:16" ht="14.25" customHeight="1">
+      <c r="C11" s="17">
+        <v>1</v>
+      </c>
+      <c r="D11" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="G11" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="22" t="s">
+      <c r="H11" s="17" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="C12" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="D12" s="22" t="s">
+      <c r="J11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="3:16" ht="14.25" customHeight="1">
+      <c r="C12" s="17">
+        <v>2</v>
+      </c>
+      <c r="D12" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="17" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="13" ht="14.25" customHeight="1">
-      <c r="C13" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="D13" s="22" t="s">
+      <c r="J12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K12" s="35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="3:16" ht="14.25" customHeight="1">
+      <c r="C13" s="17">
+        <v>3</v>
+      </c>
+      <c r="D13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" ht="14.25" customHeight="1">
-      <c r="C14" s="22">
-        <v>4.0</v>
-      </c>
-      <c r="D14" s="22" t="s">
+    <row r="14" spans="3:16" ht="14.25" customHeight="1">
+      <c r="C14" s="17">
+        <v>4</v>
+      </c>
+      <c r="D14" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="22" t="s">
+      <c r="F14" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="22" t="s">
+      <c r="H14" s="17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" ht="14.25" customHeight="1">
-      <c r="C15" s="22">
-        <v>5.0</v>
-      </c>
-      <c r="D15" s="22" t="s">
+    <row r="15" spans="3:16" ht="14.25" customHeight="1">
+      <c r="C15" s="17">
+        <v>5</v>
+      </c>
+      <c r="D15" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="22" t="s">
+      <c r="E15" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="22" t="s">
+      <c r="F15" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="G15" s="22" t="s">
+      <c r="G15" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="H15" s="22" t="s">
+      <c r="H15" s="17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" ht="14.25" customHeight="1">
-      <c r="C16" s="22">
-        <v>6.0</v>
-      </c>
-      <c r="D16" s="22" t="s">
+    <row r="16" spans="3:16" ht="14.25" customHeight="1">
+      <c r="C16" s="17">
+        <v>6</v>
+      </c>
+      <c r="D16" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="G16" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="H16" s="22" t="s">
+      <c r="H16" s="17" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="17" ht="14.25" customHeight="1">
-      <c r="C17" s="22">
-        <v>7.0</v>
-      </c>
-      <c r="D17" s="22" t="s">
+      <c r="J16" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="N16" s="36" t="s">
+        <v>4</v>
+      </c>
+      <c r="O16" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="P16" s="36" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="3:22" ht="14.25" customHeight="1">
+      <c r="C17" s="17">
+        <v>7</v>
+      </c>
+      <c r="D17" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="22" t="s">
+      <c r="E17" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="22" t="s">
+      <c r="F17" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="G17" s="22" t="s">
+      <c r="G17" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="H17" s="22" t="s">
+      <c r="H17" s="17" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" ht="14.25" customHeight="1">
-      <c r="C18" s="22">
-        <v>8.0</v>
-      </c>
-      <c r="D18" s="22" t="s">
+      <c r="J17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="K17" s="3">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3">
+        <v>3</v>
+      </c>
+      <c r="N17" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="O17" s="37">
+        <v>1</v>
+      </c>
+      <c r="P17" s="37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" ht="14.25" customHeight="1">
+      <c r="C18" s="17">
+        <v>8</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="F18" s="22" t="s">
+      <c r="F18" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="G18" s="22" t="s">
+      <c r="G18" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="H18" s="22" t="s">
+      <c r="H18" s="17" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="19" ht="14.25" customHeight="1"/>
-    <row r="20" ht="14.25" customHeight="1"/>
-    <row r="21" ht="14.25" customHeight="1">
-      <c r="C21" s="23" t="s">
+      <c r="J18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K18" s="3">
+        <v>2</v>
+      </c>
+      <c r="L18" s="3">
+        <v>1</v>
+      </c>
+      <c r="N18" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="O18" s="37">
+        <v>1</v>
+      </c>
+      <c r="P18" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" ht="14.25" customHeight="1">
+      <c r="J19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K19" s="3">
+        <v>2</v>
+      </c>
+      <c r="L19" s="3">
+        <v>0</v>
+      </c>
+      <c r="N19" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="O19" s="37">
+        <v>2</v>
+      </c>
+      <c r="P19" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="3:22" ht="14.25" customHeight="1">
+      <c r="N20" s="38"/>
+      <c r="O20" s="38"/>
+      <c r="P20" s="38"/>
+    </row>
+    <row r="21" spans="3:22" ht="14.25" customHeight="1">
+      <c r="C21" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="D21" s="24"/>
-    </row>
-    <row r="22" ht="14.25" customHeight="1">
-      <c r="C22" s="25" t="s">
+      <c r="D21" s="19"/>
+      <c r="N21" s="38"/>
+      <c r="O21" s="38"/>
+      <c r="P21" s="38"/>
+    </row>
+    <row r="22" spans="3:22" ht="14.25" customHeight="1">
+      <c r="C22" s="27" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="23" ht="14.25" customHeight="1"/>
-    <row r="24" ht="14.25" customHeight="1"/>
-    <row r="25" ht="14.25" customHeight="1">
-      <c r="C25" s="26" t="s">
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="J22" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="N22" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="O22" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="P22" s="37" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" ht="14.25" customHeight="1">
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="J23" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K23" s="7">
+        <v>2</v>
+      </c>
+      <c r="L23" s="7">
+        <v>3</v>
+      </c>
+      <c r="N23" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="O23" s="37">
+        <v>3</v>
+      </c>
+      <c r="P23" s="37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" ht="14.25" customHeight="1">
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="J24" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K24" s="7">
+        <v>2</v>
+      </c>
+      <c r="L24" s="7">
+        <v>1</v>
+      </c>
+      <c r="N24" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="O24" s="37">
+        <v>1</v>
+      </c>
+      <c r="P24" s="37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" ht="14.25" customHeight="1">
+      <c r="C25" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="D25" s="27"/>
-    </row>
-    <row r="26" ht="14.25" customHeight="1">
-      <c r="C26" s="27" t="s">
+      <c r="D25" s="20"/>
+    </row>
+    <row r="26" spans="3:22" ht="14.25" customHeight="1">
+      <c r="C26" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="D26" s="27"/>
-    </row>
-    <row r="27" ht="14.25" customHeight="1">
-      <c r="C27" s="27" t="s">
+      <c r="D26" s="20"/>
+    </row>
+    <row r="27" spans="3:22" ht="14.25" customHeight="1">
+      <c r="C27" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="D27" s="27"/>
-    </row>
-    <row r="28" ht="14.25" customHeight="1">
-      <c r="C28" s="26" t="s">
+      <c r="D27" s="20"/>
+      <c r="R27" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="S27" s="20"/>
+      <c r="T27" s="20"/>
+      <c r="U27" s="20"/>
+      <c r="V27" s="20"/>
+    </row>
+    <row r="28" spans="3:22" ht="14.25" customHeight="1">
+      <c r="C28" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="D28" s="27"/>
-    </row>
-    <row r="29" ht="14.25" customHeight="1"/>
-    <row r="30" ht="14.25" customHeight="1">
-      <c r="C30" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
-    </row>
-    <row r="31" ht="14.25" customHeight="1">
-      <c r="C31" s="27" t="s">
+      <c r="D28" s="20"/>
+      <c r="R28" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-    </row>
-    <row r="32" ht="14.25" customHeight="1">
-      <c r="C32" s="27" t="s">
+      <c r="S28" s="20"/>
+      <c r="T28" s="20"/>
+      <c r="U28" s="20"/>
+      <c r="V28" s="20"/>
+    </row>
+    <row r="29" spans="3:22" ht="14.25" customHeight="1">
+      <c r="R29" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="27"/>
-    </row>
-    <row r="33" ht="14.25" customHeight="1">
-      <c r="C33" s="27" t="s">
+      <c r="S29" s="20"/>
+      <c r="T29" s="20"/>
+      <c r="U29" s="20"/>
+      <c r="V29" s="20"/>
+    </row>
+    <row r="30" spans="3:22" ht="14.25" customHeight="1">
+      <c r="C30" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30" s="31">
+        <f>4/8</f>
+        <v>0.5</v>
+      </c>
+      <c r="H30" s="20"/>
+      <c r="R30" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="27"/>
-    </row>
-    <row r="34" ht="14.25" customHeight="1">
-      <c r="C34" s="27" t="s">
+      <c r="S30" s="20"/>
+      <c r="T30" s="20"/>
+      <c r="U30" s="20"/>
+      <c r="V30" s="20"/>
+    </row>
+    <row r="31" spans="3:22" ht="14.25" customHeight="1">
+      <c r="C31" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31" s="32">
+        <f>0/4</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="5">
+        <f>1/8</f>
+        <v>0.125</v>
+      </c>
+      <c r="R31" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="27"/>
-    </row>
-    <row r="35" ht="14.25" customHeight="1"/>
-    <row r="36" ht="14.25" customHeight="1"/>
-    <row r="37" ht="14.25" customHeight="1"/>
-    <row r="38" ht="14.25" customHeight="1"/>
-    <row r="39" ht="14.25" customHeight="1"/>
-    <row r="40" ht="14.25" customHeight="1"/>
-    <row r="41" ht="14.25" customHeight="1"/>
-    <row r="42" ht="14.25" customHeight="1"/>
-    <row r="43" ht="14.25" customHeight="1"/>
-    <row r="44" ht="14.25" customHeight="1"/>
-    <row r="45" ht="14.25" customHeight="1"/>
-    <row r="46" ht="14.25" customHeight="1"/>
-    <row r="47" ht="14.25" customHeight="1"/>
-    <row r="48" ht="14.25" customHeight="1"/>
-    <row r="49" ht="14.25" customHeight="1"/>
-    <row r="50" ht="14.25" customHeight="1"/>
-    <row r="51" ht="14.25" customHeight="1"/>
-    <row r="52" ht="14.25" customHeight="1"/>
-    <row r="53" ht="14.25" customHeight="1"/>
-    <row r="54" ht="14.25" customHeight="1"/>
-    <row r="55" ht="14.25" customHeight="1"/>
-    <row r="56" ht="14.25" customHeight="1"/>
-    <row r="57" ht="14.25" customHeight="1"/>
-    <row r="58" ht="14.25" customHeight="1"/>
-    <row r="59" ht="14.25" customHeight="1"/>
-    <row r="60" ht="14.25" customHeight="1"/>
-    <row r="61" ht="14.25" customHeight="1"/>
-    <row r="62" ht="14.25" customHeight="1"/>
-    <row r="63" ht="14.25" customHeight="1"/>
-    <row r="64" ht="14.25" customHeight="1"/>
+      <c r="S31" s="20"/>
+      <c r="T31" s="20"/>
+      <c r="U31" s="20"/>
+      <c r="V31" s="20"/>
+    </row>
+    <row r="32" spans="3:22" ht="14.25" customHeight="1">
+      <c r="C32" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32" s="33">
+        <f>2/4</f>
+        <v>0.5</v>
+      </c>
+      <c r="H32" s="20"/>
+    </row>
+    <row r="33" spans="3:8" ht="14.25" customHeight="1">
+      <c r="C33" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" s="33">
+        <f t="shared" ref="D32:D33" si="0">2/4</f>
+        <v>0.5</v>
+      </c>
+      <c r="H33" s="20"/>
+    </row>
+    <row r="34" spans="3:8" ht="14.25" customHeight="1">
+      <c r="C34" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D34" s="34">
+        <f>3/4</f>
+        <v>0.75</v>
+      </c>
+      <c r="H34" s="20"/>
+    </row>
+    <row r="35" spans="3:8" ht="14.25" customHeight="1"/>
+    <row r="36" spans="3:8" ht="14.25" customHeight="1">
+      <c r="C36" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36" s="10">
+        <f>D30*I31*D32*D33*D34</f>
+        <v>1.171875E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="3:8" ht="14.25" customHeight="1"/>
+    <row r="38" spans="3:8" ht="14.25" customHeight="1">
+      <c r="C38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+    </row>
+    <row r="39" spans="3:8" ht="14.25" customHeight="1"/>
+    <row r="40" spans="3:8" ht="14.25" customHeight="1">
+      <c r="C40" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D40" s="5">
+        <f>4/8</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="41" spans="3:8" ht="14.25" customHeight="1">
+      <c r="C41" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D41" s="5">
+        <f>3/4</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="42" spans="3:8" ht="14.25" customHeight="1">
+      <c r="C42" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D42" s="5">
+        <f>1/4</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="43" spans="3:8" ht="14.25" customHeight="1">
+      <c r="C43" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D43" s="5">
+        <f>3/4</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="44" spans="3:8" ht="14.25" customHeight="1">
+      <c r="C44" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D44" s="5">
+        <f>2/4</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="45" spans="3:8" ht="14.25" customHeight="1"/>
+    <row r="46" spans="3:8" ht="14.25" customHeight="1">
+      <c r="C46" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D46" s="10">
+        <f>D40*D41*D42*D43*D44</f>
+        <v>3.515625E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="3:8" ht="14.25" customHeight="1"/>
+    <row r="48" spans="3:8" ht="14.25" customHeight="1">
+      <c r="C48" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="49" spans="3:8" ht="14.25" customHeight="1"/>
+    <row r="50" spans="3:8" ht="14.25" customHeight="1">
+      <c r="C50" s="11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="51" spans="3:8" ht="14.25" customHeight="1"/>
+    <row r="52" spans="3:8" ht="14.25" customHeight="1">
+      <c r="C52" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="53" spans="3:8" ht="14.25" customHeight="1">
+      <c r="C53" s="12"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+    </row>
+    <row r="54" spans="3:8" ht="14.25" customHeight="1">
+      <c r="C54" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="55" spans="3:8" ht="14.25" customHeight="1"/>
+    <row r="56" spans="3:8" ht="14.25" customHeight="1">
+      <c r="C56" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="3:8" ht="14.25" customHeight="1"/>
+    <row r="58" spans="3:8" ht="14.25" customHeight="1"/>
+    <row r="59" spans="3:8" ht="14.25" customHeight="1"/>
+    <row r="60" spans="3:8" ht="14.25" customHeight="1"/>
+    <row r="61" spans="3:8" ht="14.25" customHeight="1"/>
+    <row r="62" spans="3:8" ht="14.25" customHeight="1"/>
+    <row r="63" spans="3:8" ht="14.25" customHeight="1"/>
+    <row r="64" spans="3:8" ht="14.25" customHeight="1"/>
     <row r="65" ht="14.25" customHeight="1"/>
     <row r="66" ht="14.25" customHeight="1"/>
     <row r="67" ht="14.25" customHeight="1"/>
@@ -3492,13 +3946,15 @@
     <row r="999" ht="14.25" customHeight="1"/>
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="6">
+    <mergeCell ref="E31:H31"/>
     <mergeCell ref="C2:H2"/>
     <mergeCell ref="C22:H24"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="D6:G6"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/WEEK6/cara kerja perhitungan naive bayes.xlsx
+++ b/WEEK6/cara kerja perhitungan naive bayes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\Machine-Learning\WEEK6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F724239-171E-43ED-97DC-6AB0834FA8FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E0E93EA-0774-4112-A907-1891D119715E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -462,7 +462,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -504,19 +504,20 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -526,30 +527,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="12" fontId="3" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="12" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="12" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="12" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="12" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -780,15 +790,15 @@
     <row r="1" spans="2:9" ht="14.25" customHeight="1"/>
     <row r="2" spans="2:9" ht="14.25" customHeight="1"/>
     <row r="3" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
     </row>
     <row r="4" spans="2:9" ht="14.25" customHeight="1"/>
     <row r="5" spans="2:9" ht="14.25" customHeight="1">
@@ -816,7 +826,7 @@
       <c r="G7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="29"/>
+      <c r="I7" s="21"/>
     </row>
     <row r="8" spans="2:9" ht="14.25" customHeight="1">
       <c r="B8" s="3">
@@ -837,7 +847,7 @@
       <c r="G8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="30"/>
+      <c r="I8" s="22"/>
     </row>
     <row r="9" spans="2:9" ht="14.25" customHeight="1">
       <c r="B9" s="3">
@@ -993,22 +1003,22 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="14.25" customHeight="1">
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
     </row>
     <row r="25" spans="2:8" ht="14.25" customHeight="1">
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
     </row>
     <row r="26" spans="2:8" ht="14.25" customHeight="1">
       <c r="B26" s="6"/>
@@ -1201,14 +1211,14 @@
       </c>
     </row>
     <row r="47" spans="2:8" ht="14.25" customHeight="1">
-      <c r="B47" s="24" t="s">
+      <c r="B47" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="C47" s="22"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="22"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="22"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
+      <c r="G47" s="26"/>
     </row>
     <row r="48" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="49" spans="2:8" ht="14.25" customHeight="1">
@@ -1254,9 +1264,9 @@
       <c r="D53" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="E53" s="22"/>
-      <c r="F53" s="22"/>
-      <c r="G53" s="22"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="26"/>
+      <c r="G53" s="26"/>
       <c r="H53" s="5">
         <f>1/7</f>
         <v>0.14285714285714285</v>
@@ -2348,7 +2358,7 @@
   <cols>
     <col min="1" max="2" width="8.6640625" customWidth="1"/>
     <col min="3" max="3" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.6640625" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" customWidth="1"/>
     <col min="5" max="5" width="13.109375" customWidth="1"/>
     <col min="6" max="13" width="8.6640625" customWidth="1"/>
     <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
@@ -2357,48 +2367,48 @@
   <sheetData>
     <row r="1" spans="3:16" ht="14.25" customHeight="1"/>
     <row r="2" spans="3:16" ht="14.25" customHeight="1">
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="3:16" ht="14.25" customHeight="1"/>
     <row r="4" spans="3:16" ht="14.25" customHeight="1">
       <c r="C4" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
     </row>
     <row r="5" spans="3:16" ht="14.25" customHeight="1">
       <c r="C5" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="29">
         <v>4222311024</v>
       </c>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
     </row>
     <row r="6" spans="3:16" ht="14.25" customHeight="1">
       <c r="C6" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
     </row>
     <row r="7" spans="3:16" ht="14.25" customHeight="1"/>
     <row r="8" spans="3:16" ht="14.25" customHeight="1">
@@ -2446,10 +2456,10 @@
       <c r="H11" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="K11" s="35" t="s">
+      <c r="K11" s="34" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2472,10 +2482,10 @@
       <c r="H12" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="J12" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="K12" s="35" t="s">
+      <c r="K12" s="34" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2567,13 +2577,13 @@
       <c r="L16" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="N16" s="36" t="s">
+      <c r="N16" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="O16" s="36" t="s">
+      <c r="O16" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="P16" s="36" t="s">
+      <c r="P16" s="23" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2605,13 +2615,13 @@
       <c r="L17" s="3">
         <v>3</v>
       </c>
-      <c r="N17" s="37" t="s">
+      <c r="N17" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="O17" s="37">
+      <c r="O17" s="24">
         <v>1</v>
       </c>
-      <c r="P17" s="37">
+      <c r="P17" s="24">
         <v>2</v>
       </c>
     </row>
@@ -2643,13 +2653,13 @@
       <c r="L18" s="3">
         <v>1</v>
       </c>
-      <c r="N18" s="37" t="s">
+      <c r="N18" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="O18" s="37">
+      <c r="O18" s="24">
         <v>1</v>
       </c>
-      <c r="P18" s="37">
+      <c r="P18" s="24">
         <v>1</v>
       </c>
     </row>
@@ -2663,39 +2673,32 @@
       <c r="L19" s="3">
         <v>0</v>
       </c>
-      <c r="N19" s="37" t="s">
+      <c r="N19" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="O19" s="37">
+      <c r="O19" s="24">
         <v>2</v>
       </c>
-      <c r="P19" s="37">
+      <c r="P19" s="24">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="3:22" ht="14.25" customHeight="1">
-      <c r="N20" s="38"/>
-      <c r="O20" s="38"/>
-      <c r="P20" s="38"/>
-    </row>
+    <row r="20" spans="3:22" ht="14.25" customHeight="1"/>
     <row r="21" spans="3:22" ht="14.25" customHeight="1">
       <c r="C21" s="18" t="s">
         <v>61</v>
       </c>
       <c r="D21" s="19"/>
-      <c r="N21" s="38"/>
-      <c r="O21" s="38"/>
-      <c r="P21" s="38"/>
     </row>
     <row r="22" spans="3:22" ht="14.25" customHeight="1">
-      <c r="C22" s="27" t="s">
+      <c r="C22" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
       <c r="J22" s="7" t="s">
         <v>5</v>
       </c>
@@ -2705,23 +2708,23 @@
       <c r="L22" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="N22" s="37" t="s">
+      <c r="N22" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="O22" s="37" t="s">
+      <c r="O22" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="P22" s="37" t="s">
+      <c r="P22" s="24" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="23" spans="3:22" ht="14.25" customHeight="1">
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
       <c r="J23" s="7" t="s">
         <v>10</v>
       </c>
@@ -2731,23 +2734,23 @@
       <c r="L23" s="7">
         <v>3</v>
       </c>
-      <c r="N23" s="37" t="s">
+      <c r="N23" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="O23" s="37">
+      <c r="O23" s="24">
         <v>3</v>
       </c>
-      <c r="P23" s="37">
+      <c r="P23" s="24">
         <v>2</v>
       </c>
     </row>
     <row r="24" spans="3:22" ht="14.25" customHeight="1">
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
       <c r="J24" s="7" t="s">
         <v>19</v>
       </c>
@@ -2757,13 +2760,13 @@
       <c r="L24" s="7">
         <v>1</v>
       </c>
-      <c r="N24" s="37" t="s">
+      <c r="N24" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="O24" s="37">
+      <c r="O24" s="24">
         <v>1</v>
       </c>
-      <c r="P24" s="37">
+      <c r="P24" s="24">
         <v>2</v>
       </c>
     </row>
@@ -2815,10 +2818,10 @@
       <c r="V29" s="20"/>
     </row>
     <row r="30" spans="3:22" ht="14.25" customHeight="1">
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="D30" s="31">
+      <c r="D30" s="35">
         <f>4/8</f>
         <v>0.5</v>
       </c>
@@ -2832,19 +2835,19 @@
       <c r="V30" s="20"/>
     </row>
     <row r="31" spans="3:22" ht="14.25" customHeight="1">
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="D31" s="32">
+      <c r="D31" s="36">
         <f>0/4</f>
         <v>0</v>
       </c>
       <c r="E31" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
       <c r="I31" s="5">
         <f>1/8</f>
         <v>0.125</v>
@@ -2858,45 +2861,45 @@
       <c r="V31" s="20"/>
     </row>
     <row r="32" spans="3:22" ht="14.25" customHeight="1">
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="D32" s="33">
+      <c r="D32" s="37">
         <f>2/4</f>
         <v>0.5</v>
       </c>
       <c r="H32" s="20"/>
     </row>
     <row r="33" spans="3:8" ht="14.25" customHeight="1">
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="D33" s="33">
-        <f t="shared" ref="D32:D33" si="0">2/4</f>
+      <c r="D33" s="37">
+        <f t="shared" ref="D33" si="0">2/4</f>
         <v>0.5</v>
       </c>
       <c r="H33" s="20"/>
     </row>
     <row r="34" spans="3:8" ht="14.25" customHeight="1">
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="D34" s="34">
+      <c r="D34" s="38">
         <f>3/4</f>
         <v>0.75</v>
       </c>
       <c r="H34" s="20"/>
     </row>
-    <row r="35" spans="3:8" ht="14.25" customHeight="1"/>
-    <row r="36" spans="3:8" ht="14.25" customHeight="1">
-      <c r="C36" s="4" t="s">
+    <row r="35" spans="3:8" ht="14.25" customHeight="1">
+      <c r="C35" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="D36" s="10">
+      <c r="D35" s="39">
         <f>D30*I31*D32*D33*D34</f>
         <v>1.171875E-2</v>
       </c>
     </row>
+    <row r="36" spans="3:8" ht="14.25" customHeight="1"/>
     <row r="37" spans="3:8" ht="14.25" customHeight="1"/>
     <row r="38" spans="3:8" ht="14.25" customHeight="1">
       <c r="C38" s="1" t="s">
@@ -2910,60 +2913,60 @@
     </row>
     <row r="39" spans="3:8" ht="14.25" customHeight="1"/>
     <row r="40" spans="3:8" ht="14.25" customHeight="1">
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="D40" s="5">
+      <c r="D40" s="41">
         <f>4/8</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="41" spans="3:8" ht="14.25" customHeight="1">
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="D41" s="5">
+      <c r="D41" s="41">
         <f>3/4</f>
         <v>0.75</v>
       </c>
     </row>
     <row r="42" spans="3:8" ht="14.25" customHeight="1">
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="D42" s="5">
+      <c r="D42" s="41">
         <f>1/4</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="43" spans="3:8" ht="14.25" customHeight="1">
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="D43" s="5">
+      <c r="D43" s="41">
         <f>3/4</f>
         <v>0.75</v>
       </c>
     </row>
     <row r="44" spans="3:8" ht="14.25" customHeight="1">
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="40" t="s">
         <v>75</v>
       </c>
-      <c r="D44" s="5">
+      <c r="D44" s="41">
         <f>2/4</f>
         <v>0.5</v>
       </c>
     </row>
-    <row r="45" spans="3:8" ht="14.25" customHeight="1"/>
-    <row r="46" spans="3:8" ht="14.25" customHeight="1">
-      <c r="C46" s="4" t="s">
+    <row r="45" spans="3:8" ht="14.25" customHeight="1">
+      <c r="C45" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="D46" s="10">
+      <c r="D45" s="42">
         <f>D40*D41*D42*D43*D44</f>
         <v>3.515625E-2</v>
       </c>
     </row>
+    <row r="46" spans="3:8" ht="14.25" customHeight="1"/>
     <row r="47" spans="3:8" ht="14.25" customHeight="1"/>
     <row r="48" spans="3:8" ht="14.25" customHeight="1">
       <c r="C48" s="1" t="s">
